--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/3.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/3.xlsx
@@ -426,13 +426,13 @@
         <v>-11.72280068219569</v>
       </c>
       <c r="E2">
-        <v>-3.344203147314031</v>
+        <v>-3.716855801879232</v>
       </c>
       <c r="F2">
-        <v>-1.648655885567015</v>
+        <v>-0.8861138700635697</v>
       </c>
       <c r="G2">
-        <v>-5.470152886161237</v>
+        <v>-5.232861505425314</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.24606890481562</v>
       </c>
       <c r="E3">
-        <v>-3.756004459675542</v>
+        <v>-4.321945970310137</v>
       </c>
       <c r="F3">
-        <v>-1.814982948007725</v>
+        <v>-1.040949819892645</v>
       </c>
       <c r="G3">
-        <v>-5.920320078009254</v>
+        <v>-5.589668100242451</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.89698403869113</v>
       </c>
       <c r="E4">
-        <v>-4.724205787937487</v>
+        <v>-5.298801212400741</v>
       </c>
       <c r="F4">
-        <v>-1.680405551381515</v>
+        <v>-0.7509541311531912</v>
       </c>
       <c r="G4">
-        <v>-5.38096928417553</v>
+        <v>-5.305222284475748</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.71320983448067</v>
       </c>
       <c r="E5">
-        <v>-4.920084931139269</v>
+        <v>-6.444677218353632</v>
       </c>
       <c r="F5">
-        <v>-1.592981312424861</v>
+        <v>-0.7301471987296732</v>
       </c>
       <c r="G5">
-        <v>-5.409253414017942</v>
+        <v>-4.951385195169908</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.6672949753262</v>
       </c>
       <c r="E6">
-        <v>-6.403209981865396</v>
+        <v>-7.015269471794105</v>
       </c>
       <c r="F6">
-        <v>-1.222442632743808</v>
+        <v>-0.592374789030865</v>
       </c>
       <c r="G6">
-        <v>-5.553879816693588</v>
+        <v>-5.552432797985873</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.72487623358185</v>
       </c>
       <c r="E7">
-        <v>-6.28855354846519</v>
+        <v>-7.489962231174143</v>
       </c>
       <c r="F7">
-        <v>-1.139931440853158</v>
+        <v>-0.6602843487123685</v>
       </c>
       <c r="G7">
-        <v>-5.765151110463114</v>
+        <v>-5.123354017100405</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.86045598017658</v>
       </c>
       <c r="E8">
-        <v>-6.925709841344409</v>
+        <v>-7.760796676150884</v>
       </c>
       <c r="F8">
-        <v>-1.06611147975268</v>
+        <v>-0.2227448283906836</v>
       </c>
       <c r="G8">
-        <v>-5.603547667438902</v>
+        <v>-5.080819542025324</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.03092088428549</v>
       </c>
       <c r="E9">
-        <v>-8.027396997930454</v>
+        <v>-10.29693684482861</v>
       </c>
       <c r="F9">
-        <v>-1.091756077808547</v>
+        <v>-0.3254888940947119</v>
       </c>
       <c r="G9">
-        <v>-4.748641796233379</v>
+        <v>-4.871172452927722</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.21268733752054</v>
       </c>
       <c r="E10">
-        <v>-8.664254411525166</v>
+        <v>-9.553868601858001</v>
       </c>
       <c r="F10">
-        <v>-0.7839612586851402</v>
+        <v>-0.01095944798654521</v>
       </c>
       <c r="G10">
-        <v>-5.27667237568702</v>
+        <v>-4.86315314743644</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.36690228168744</v>
       </c>
       <c r="E11">
-        <v>-8.607385834936842</v>
+        <v>-10.38559983742479</v>
       </c>
       <c r="F11">
-        <v>-0.7253376975890192</v>
+        <v>0.4217896236447501</v>
       </c>
       <c r="G11">
-        <v>-4.816727143591857</v>
+        <v>-3.726879246286972</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.47992624202124</v>
       </c>
       <c r="E12">
-        <v>-9.57838123166152</v>
+        <v>-10.73730829970452</v>
       </c>
       <c r="F12">
-        <v>-0.2001461372749103</v>
+        <v>0.3752577415272935</v>
       </c>
       <c r="G12">
-        <v>-4.467112986433022</v>
+        <v>-4.50027629273433</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.52468899513313</v>
       </c>
       <c r="E13">
-        <v>-9.874996279163929</v>
+        <v>-11.35591143457431</v>
       </c>
       <c r="F13">
-        <v>-0.08858492893548409</v>
+        <v>0.8622350568154556</v>
       </c>
       <c r="G13">
-        <v>-4.144805155091887</v>
+        <v>-3.730163749067977</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.50008423955455</v>
       </c>
       <c r="E14">
-        <v>-11.01408863105333</v>
+        <v>-11.75493339328618</v>
       </c>
       <c r="F14">
-        <v>-0.03201406226350025</v>
+        <v>1.090198452596268</v>
       </c>
       <c r="G14">
-        <v>-3.659249988725258</v>
+        <v>-3.230217144941623</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.39550109295745</v>
       </c>
       <c r="E15">
-        <v>-11.62980712798024</v>
+        <v>-12.37518942116877</v>
       </c>
       <c r="F15">
-        <v>0.03486500836892064</v>
+        <v>0.7821766608044947</v>
       </c>
       <c r="G15">
-        <v>-3.26007626113257</v>
+        <v>-4.032147694069912</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.2232943794293</v>
       </c>
       <c r="E16">
-        <v>-12.67148294701664</v>
+        <v>-13.45187487275847</v>
       </c>
       <c r="F16">
-        <v>0.6284722608476435</v>
+        <v>0.9994706844372497</v>
       </c>
       <c r="G16">
-        <v>-2.274351367573545</v>
+        <v>-2.89690737771167</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.99317369866407</v>
       </c>
       <c r="E17">
-        <v>-13.19449452405851</v>
+        <v>-14.71231674263141</v>
       </c>
       <c r="F17">
-        <v>0.6813858854362675</v>
+        <v>1.377123383373544</v>
       </c>
       <c r="G17">
-        <v>-1.969404479503432</v>
+        <v>-1.429722282292202</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.72947962970792</v>
       </c>
       <c r="E18">
-        <v>-14.69913888326909</v>
+        <v>-14.41990864748213</v>
       </c>
       <c r="F18">
-        <v>0.7486393781347539</v>
+        <v>1.461820636840183</v>
       </c>
       <c r="G18">
-        <v>-1.885759579510067</v>
+        <v>-1.724576132845464</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.45383591312418</v>
       </c>
       <c r="E19">
-        <v>-15.15439996068222</v>
+        <v>-16.64780917587976</v>
       </c>
       <c r="F19">
-        <v>0.9871644583012603</v>
+        <v>1.677635196291538</v>
       </c>
       <c r="G19">
-        <v>-1.063475613048543</v>
+        <v>-1.37649758737645</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.19192881161444</v>
       </c>
       <c r="E20">
-        <v>-16.02336883801408</v>
+        <v>-16.6427553988872</v>
       </c>
       <c r="F20">
-        <v>1.340052285363461</v>
+        <v>2.106712943593626</v>
       </c>
       <c r="G20">
-        <v>-0.7480944404193951</v>
+        <v>-0.6962150463430147</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.966053987265772</v>
       </c>
       <c r="E21">
-        <v>-16.43368933937508</v>
+        <v>-19.04004349754174</v>
       </c>
       <c r="F21">
-        <v>1.900505789279939</v>
+        <v>2.36534084389127</v>
       </c>
       <c r="G21">
-        <v>-0.208057871279746</v>
+        <v>-0.6668382697213061</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.789698247188268</v>
       </c>
       <c r="E22">
-        <v>-17.80665020291661</v>
+        <v>-18.54824216336073</v>
       </c>
       <c r="F22">
-        <v>1.928153379715775</v>
+        <v>2.43178750673943</v>
       </c>
       <c r="G22">
-        <v>-0.4866368628981618</v>
+        <v>-0.2259044353415658</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.671932460459516</v>
       </c>
       <c r="E23">
-        <v>-18.80132951870141</v>
+        <v>-19.02258170176816</v>
       </c>
       <c r="F23">
-        <v>2.113972755511761</v>
+        <v>2.728916267184391</v>
       </c>
       <c r="G23">
-        <v>-0.2564329207306394</v>
+        <v>0.514847737810876</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.606773920465494</v>
       </c>
       <c r="E24">
-        <v>-18.46391292038989</v>
+        <v>-19.73886854945742</v>
       </c>
       <c r="F24">
-        <v>2.205219081664932</v>
+        <v>2.432839533340986</v>
       </c>
       <c r="G24">
-        <v>-0.4016105686282709</v>
+        <v>-0.744921499171412</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.58938544062042</v>
       </c>
       <c r="E25">
-        <v>-19.06922951252118</v>
+        <v>-19.1770479501698</v>
       </c>
       <c r="F25">
-        <v>2.45229622689794</v>
+        <v>2.925477911459879</v>
       </c>
       <c r="G25">
-        <v>0.2757418415525801</v>
+        <v>0.3964218892873973</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.596827242376257</v>
       </c>
       <c r="E26">
-        <v>-18.56720741250485</v>
+        <v>-20.50987294858135</v>
       </c>
       <c r="F26">
-        <v>2.281470301092626</v>
+        <v>3.269218905660368</v>
       </c>
       <c r="G26">
-        <v>-0.6331893426292006</v>
+        <v>-0.2678187595419126</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.613336547729755</v>
       </c>
       <c r="E27">
-        <v>-18.79889319968528</v>
+        <v>-19.70750433848029</v>
       </c>
       <c r="F27">
-        <v>2.455506978951191</v>
+        <v>2.751648325452015</v>
       </c>
       <c r="G27">
-        <v>-1.090811469860277</v>
+        <v>-0.1590659521756769</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.606795852291732</v>
       </c>
       <c r="E28">
-        <v>-18.45054939359325</v>
+        <v>-20.23822790675723</v>
       </c>
       <c r="F28">
-        <v>2.572257080701753</v>
+        <v>3.313027944124823</v>
       </c>
       <c r="G28">
-        <v>-0.5321670932570167</v>
+        <v>-0.2709162326940284</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.559459174569028</v>
       </c>
       <c r="E29">
-        <v>-18.87421530785486</v>
+        <v>-19.86380461885503</v>
       </c>
       <c r="F29">
-        <v>2.568599010250991</v>
+        <v>3.122495157806908</v>
       </c>
       <c r="G29">
-        <v>-1.467078989746481</v>
+        <v>-0.8254623635695421</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.443738339765789</v>
       </c>
       <c r="E30">
-        <v>-18.68680441104742</v>
+        <v>-20.26031327449264</v>
       </c>
       <c r="F30">
-        <v>2.508663315188835</v>
+        <v>2.572227259475253</v>
       </c>
       <c r="G30">
-        <v>-1.17393137440413</v>
+        <v>-1.003471914390977</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.256197274245071</v>
       </c>
       <c r="E31">
-        <v>-18.41734209369501</v>
+        <v>-19.18411236962177</v>
       </c>
       <c r="F31">
-        <v>2.206599141757996</v>
+        <v>2.389635203080574</v>
       </c>
       <c r="G31">
-        <v>-1.517537614887621</v>
+        <v>0.07144642481843323</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.989632921160137</v>
       </c>
       <c r="E32">
-        <v>-18.11054703662336</v>
+        <v>-19.12227605704703</v>
       </c>
       <c r="F32">
-        <v>2.071436089378006</v>
+        <v>2.503134791142552</v>
       </c>
       <c r="G32">
-        <v>-2.151397433298033</v>
+        <v>-0.433146389036094</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.663055750014699</v>
       </c>
       <c r="E33">
-        <v>-17.51093632174173</v>
+        <v>-19.2430504588316</v>
       </c>
       <c r="F33">
-        <v>2.051914783163633</v>
+        <v>2.994663156941694</v>
       </c>
       <c r="G33">
-        <v>-1.621742649172467</v>
+        <v>-0.5456397889800967</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.287778975886667</v>
       </c>
       <c r="E34">
-        <v>-16.95372118051992</v>
+        <v>-18.93590218078735</v>
       </c>
       <c r="F34">
-        <v>2.108242109819193</v>
+        <v>2.490707623365753</v>
       </c>
       <c r="G34">
-        <v>-2.350869454339796</v>
+        <v>-1.09138240241162</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.894811191118179</v>
       </c>
       <c r="E35">
-        <v>-17.29100645308521</v>
+        <v>-18.93318962485675</v>
       </c>
       <c r="F35">
-        <v>2.145124340061439</v>
+        <v>2.256741877384255</v>
       </c>
       <c r="G35">
-        <v>-1.557975389386218</v>
+        <v>-1.307378655226747</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.499059943886444</v>
       </c>
       <c r="E36">
-        <v>-16.97110146376136</v>
+        <v>-19.02264510040427</v>
       </c>
       <c r="F36">
-        <v>2.057711698248424</v>
+        <v>2.265476183279374</v>
       </c>
       <c r="G36">
-        <v>-2.066400670022177</v>
+        <v>-1.697847302022228</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.130483505414092</v>
       </c>
       <c r="E37">
-        <v>-16.39548260417237</v>
+        <v>-18.69029586450734</v>
       </c>
       <c r="F37">
-        <v>1.832937516968389</v>
+        <v>2.52103912418666</v>
       </c>
       <c r="G37">
-        <v>-2.102868166433845</v>
+        <v>-0.8492184076599217</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.798551864532825</v>
       </c>
       <c r="E38">
-        <v>-16.07912340999652</v>
+        <v>-18.63933241802502</v>
       </c>
       <c r="F38">
-        <v>1.911922348825322</v>
+        <v>2.807120776947886</v>
       </c>
       <c r="G38">
-        <v>-1.928451553220002</v>
+        <v>-0.6213605389074024</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.526271616067968</v>
       </c>
       <c r="E39">
-        <v>-15.00803968075431</v>
+        <v>-16.53764951716917</v>
       </c>
       <c r="F39">
-        <v>2.010975209382476</v>
+        <v>2.190122914116313</v>
       </c>
       <c r="G39">
-        <v>-1.040241283186115</v>
+        <v>-0.0366370133496757</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.314195375476284</v>
       </c>
       <c r="E40">
-        <v>-15.32838393205691</v>
+        <v>-17.66638977747704</v>
       </c>
       <c r="F40">
-        <v>1.894962354620405</v>
+        <v>2.517561637829708</v>
       </c>
       <c r="G40">
-        <v>-1.225351397462188</v>
+        <v>-0.314710696847937</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.176142099536403</v>
       </c>
       <c r="E41">
-        <v>-14.77050763362998</v>
+        <v>-16.28153714119137</v>
       </c>
       <c r="F41">
-        <v>1.759723092439358</v>
+        <v>2.549467036715933</v>
       </c>
       <c r="G41">
-        <v>-0.948649264575775</v>
+        <v>0.5067890576608798</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.103194852435739</v>
       </c>
       <c r="E42">
-        <v>-14.74086424277577</v>
+        <v>-15.9872497293289</v>
       </c>
       <c r="F42">
-        <v>1.593353783261105</v>
+        <v>2.10463705488221</v>
       </c>
       <c r="G42">
-        <v>-0.743172608080228</v>
+        <v>-0.3738448717922497</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.100216539453678</v>
       </c>
       <c r="E43">
-        <v>-14.55800899082004</v>
+        <v>-15.41115990844312</v>
       </c>
       <c r="F43">
-        <v>1.729746132866849</v>
+        <v>2.260505978862577</v>
       </c>
       <c r="G43">
-        <v>-0.3220245397039393</v>
+        <v>-0.7828097645183202</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.151815140734979</v>
       </c>
       <c r="E44">
-        <v>-14.39835311120562</v>
+        <v>-15.70128112421853</v>
       </c>
       <c r="F44">
-        <v>1.608688520621729</v>
+        <v>2.210777426937717</v>
       </c>
       <c r="G44">
-        <v>0.3348957038262494</v>
+        <v>-0.3056578065654291</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.257676720938218</v>
       </c>
       <c r="E45">
-        <v>-13.39847510726002</v>
+        <v>-14.80944798162193</v>
       </c>
       <c r="F45">
-        <v>1.737357172563771</v>
+        <v>2.393336348636283</v>
       </c>
       <c r="G45">
-        <v>-0.3450029342847307</v>
+        <v>0.1860266816742427</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.401085351155624</v>
       </c>
       <c r="E46">
-        <v>-12.79083087948879</v>
+        <v>-14.50428770366705</v>
       </c>
       <c r="F46">
-        <v>1.496605440818539</v>
+        <v>2.430952512397408</v>
       </c>
       <c r="G46">
-        <v>-0.1780478188970646</v>
+        <v>0.5535628709907642</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.579708990862962</v>
       </c>
       <c r="E47">
-        <v>-12.27382405898108</v>
+        <v>-14.66326431218033</v>
       </c>
       <c r="F47">
-        <v>1.339000258761905</v>
+        <v>2.214513363924342</v>
       </c>
       <c r="G47">
-        <v>0.03108411841570379</v>
+        <v>0.06362727384227648</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.778835673088592</v>
       </c>
       <c r="E48">
-        <v>-12.14805475036605</v>
+        <v>-13.08409938469953</v>
       </c>
       <c r="F48">
-        <v>1.129473007897799</v>
+        <v>2.173520774629406</v>
       </c>
       <c r="G48">
-        <v>0.2133001952763472</v>
+        <v>0.7471746303273591</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.993694171214658</v>
       </c>
       <c r="E49">
-        <v>-12.3870721369649</v>
+        <v>-12.87960708393516</v>
       </c>
       <c r="F49">
-        <v>1.178063383011212</v>
+        <v>2.099984943548088</v>
       </c>
       <c r="G49">
-        <v>0.3013878692612</v>
+        <v>0.2305397333496697</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.210538694828121</v>
       </c>
       <c r="E50">
-        <v>-12.22120319101195</v>
+        <v>-12.6019753994729</v>
       </c>
       <c r="F50">
-        <v>1.105751878951232</v>
+        <v>2.484948813181491</v>
       </c>
       <c r="G50">
-        <v>0.6707681050941294</v>
+        <v>-0.3756068877696715</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.420752956831309</v>
       </c>
       <c r="E51">
-        <v>-11.34939043200327</v>
+        <v>-12.02748865838583</v>
       </c>
       <c r="F51">
-        <v>1.312187662668091</v>
+        <v>2.163311974757305</v>
       </c>
       <c r="G51">
-        <v>0.1063520597678061</v>
+        <v>0.1942362980159734</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.614596364423752</v>
       </c>
       <c r="E52">
-        <v>-10.43506888748458</v>
+        <v>-13.22611232958007</v>
       </c>
       <c r="F52">
-        <v>1.1290886454229</v>
+        <v>1.817344328978091</v>
       </c>
       <c r="G52">
-        <v>0.1306495054154942</v>
+        <v>0.568229931361482</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.787469219084745</v>
       </c>
       <c r="E53">
-        <v>-9.853255075453104</v>
+        <v>-11.40927044380669</v>
       </c>
       <c r="F53">
-        <v>1.023417129317378</v>
+        <v>2.023864606170036</v>
       </c>
       <c r="G53">
-        <v>-0.3487960264074487</v>
+        <v>-0.7567568653363291</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.938715085232081</v>
       </c>
       <c r="E54">
-        <v>-9.487173236673032</v>
+        <v>-10.10500653096152</v>
       </c>
       <c r="F54">
-        <v>0.7927052104940764</v>
+        <v>1.941380750403678</v>
       </c>
       <c r="G54">
-        <v>-0.2895929458103877</v>
+        <v>-0.2066797582247792</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.067085619728331</v>
       </c>
       <c r="E55">
-        <v>-10.07472462527223</v>
+        <v>-11.38325436063263</v>
       </c>
       <c r="F55">
-        <v>0.9286999437464768</v>
+        <v>2.147014674474627</v>
       </c>
       <c r="G55">
-        <v>-0.3285935452659476</v>
+        <v>-0.2862329749335163</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.177373431520662</v>
       </c>
       <c r="E56">
-        <v>-9.327648682804828</v>
+        <v>-11.28101047448744</v>
       </c>
       <c r="F56">
-        <v>1.034911555398624</v>
+        <v>1.726349826515371</v>
       </c>
       <c r="G56">
-        <v>-0.3036168867554545</v>
+        <v>-0.3317992987295251</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.268143918616721</v>
       </c>
       <c r="E57">
-        <v>-9.365733149209335</v>
+        <v>-9.772372001202102</v>
       </c>
       <c r="F57">
-        <v>0.8252998110594313</v>
+        <v>1.87287807966177</v>
       </c>
       <c r="G57">
-        <v>-0.8350960300680718</v>
+        <v>-0.9464213151369121</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.346489062549608</v>
       </c>
       <c r="E58">
-        <v>-8.065562976867099</v>
+        <v>-10.29209590611442</v>
       </c>
       <c r="F58">
-        <v>0.8462028341016741</v>
+        <v>1.510059784174809</v>
       </c>
       <c r="G58">
-        <v>-0.785700520712191</v>
+        <v>-0.6248287900957354</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.408519884990222</v>
       </c>
       <c r="E59">
-        <v>-7.35026333651152</v>
+        <v>-10.05455480204207</v>
       </c>
       <c r="F59">
-        <v>0.9238490242356828</v>
+        <v>1.854948895595578</v>
       </c>
       <c r="G59">
-        <v>-0.9906226507641918</v>
+        <v>-0.06228304105829559</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.461690646441964</v>
       </c>
       <c r="E60">
-        <v>-9.170814042497181</v>
+        <v>-8.978480694443405</v>
       </c>
       <c r="F60">
-        <v>0.7862273774041842</v>
+        <v>1.701929555480842</v>
       </c>
       <c r="G60">
-        <v>-1.790755090477905</v>
+        <v>-0.4043208576363722</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.499074217484686</v>
       </c>
       <c r="E61">
-        <v>-8.258000479823052</v>
+        <v>-9.100812891286612</v>
       </c>
       <c r="F61">
-        <v>0.9584449604462014</v>
+        <v>2.0843354265744</v>
       </c>
       <c r="G61">
-        <v>-1.856825767798883</v>
+        <v>-1.521402893884647</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.528181493458238</v>
       </c>
       <c r="E62">
-        <v>-7.821315202789391</v>
+        <v>-9.272949245266178</v>
       </c>
       <c r="F62">
-        <v>0.6764040838758314</v>
+        <v>1.454847440043416</v>
       </c>
       <c r="G62">
-        <v>-1.526354257217849</v>
+        <v>-1.425515756252994</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.54044983151433</v>
       </c>
       <c r="E63">
-        <v>-7.238219832613741</v>
+        <v>-8.384263392104916</v>
       </c>
       <c r="F63">
-        <v>0.5808585309021308</v>
+        <v>1.420362505064873</v>
       </c>
       <c r="G63">
-        <v>-2.244492251382598</v>
+        <v>-1.786519033444661</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.542669192709804</v>
       </c>
       <c r="E64">
-        <v>-7.184657042051016</v>
+        <v>-8.666165427556404</v>
       </c>
       <c r="F64">
-        <v>0.5449057288858267</v>
+        <v>1.331160589661811</v>
       </c>
       <c r="G64">
-        <v>-1.933140418828449</v>
+        <v>-2.285582988971524</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.525309551139102</v>
       </c>
       <c r="E65">
-        <v>-7.557880284341183</v>
+        <v>-8.818756887718864</v>
       </c>
       <c r="F65">
-        <v>0.5545562091284408</v>
+        <v>1.294536810049239</v>
       </c>
       <c r="G65">
-        <v>-2.088466885009443</v>
+        <v>-2.721489991922196</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.495934785002715</v>
       </c>
       <c r="E66">
-        <v>-7.311798478290368</v>
+        <v>-9.43275003604885</v>
       </c>
       <c r="F66">
-        <v>0.3074243916468476</v>
+        <v>1.342936660660009</v>
       </c>
       <c r="G66">
-        <v>-2.362816382037734</v>
+        <v>-2.764936646590803</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.446605999992551</v>
       </c>
       <c r="E67">
-        <v>-6.997880131604651</v>
+        <v>-8.758242889554365</v>
       </c>
       <c r="F67">
-        <v>0.3681114159433421</v>
+        <v>1.368857933428411</v>
       </c>
       <c r="G67">
-        <v>-2.664242519374564</v>
+        <v>-2.877174111253169</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.389668015837836</v>
       </c>
       <c r="E68">
-        <v>-6.812470820308604</v>
+        <v>-8.183783319311342</v>
       </c>
       <c r="F68">
-        <v>0.3396710779030268</v>
+        <v>1.138613213820288</v>
       </c>
       <c r="G68">
-        <v>-2.573040966129798</v>
+        <v>-2.083003651112967</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.323315635886724</v>
       </c>
       <c r="E69">
-        <v>-7.461844936060518</v>
+        <v>-8.565470279521845</v>
       </c>
       <c r="F69">
-        <v>0.1651696859314913</v>
+        <v>1.019616579673334</v>
       </c>
       <c r="G69">
-        <v>-3.343921315641061</v>
+        <v>-1.871765169559035</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.263618053202354</v>
       </c>
       <c r="E70">
-        <v>-7.103126396016918</v>
+        <v>-8.506672573006254</v>
       </c>
       <c r="F70">
-        <v>0.1325552045484691</v>
+        <v>0.4252778787779388</v>
       </c>
       <c r="G70">
-        <v>-2.383041831730151</v>
+        <v>-3.199691940774109</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.206524814883212</v>
       </c>
       <c r="E71">
-        <v>-6.735468648282177</v>
+        <v>-9.746962733545065</v>
       </c>
       <c r="F71">
-        <v>0.2191237399780315</v>
+        <v>0.7795954679773713</v>
       </c>
       <c r="G71">
-        <v>-3.551875294413989</v>
+        <v>-2.305893750424487</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.163385640681593</v>
       </c>
       <c r="E72">
-        <v>-7.522771025359715</v>
+        <v>-8.490388180474671</v>
       </c>
       <c r="F72">
-        <v>0.07847275355449501</v>
+        <v>0.8394002809898845</v>
       </c>
       <c r="G72">
-        <v>-2.661610979683889</v>
+        <v>-2.920000615047041</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.125857742051128</v>
       </c>
       <c r="E73">
-        <v>-7.412837790349509</v>
+        <v>-8.435299294171362</v>
       </c>
       <c r="F73">
-        <v>0.006741935043877424</v>
+        <v>1.083253420291197</v>
       </c>
       <c r="G73">
-        <v>-2.489737313178615</v>
+        <v>-2.675152581059717</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.10237104637619</v>
       </c>
       <c r="E74">
-        <v>-7.80640746635614</v>
+        <v>-9.112392199324225</v>
       </c>
       <c r="F74">
-        <v>-0.07420861265989866</v>
+        <v>0.8160104990044377</v>
       </c>
       <c r="G74">
-        <v>-2.805627075149477</v>
+        <v>-2.462033959552223</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.082945259044402</v>
       </c>
       <c r="E75">
-        <v>-8.154330124365453</v>
+        <v>-9.136633120687284</v>
       </c>
       <c r="F75">
-        <v>-0.4586978277714976</v>
+        <v>0.4560318469742733</v>
       </c>
       <c r="G75">
-        <v>-2.680126912943835</v>
+        <v>-2.544559962993818</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.07511822814751</v>
       </c>
       <c r="E76">
-        <v>-8.376904621842451</v>
+        <v>-11.03758688267913</v>
       </c>
       <c r="F76">
-        <v>-0.5218699542763907</v>
+        <v>0.297366354642056</v>
       </c>
       <c r="G76">
-        <v>-2.608199255139248</v>
+        <v>-1.774191484045828</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.070125633957819</v>
       </c>
       <c r="E77">
-        <v>-9.327413202156428</v>
+        <v>-10.64479157572781</v>
       </c>
       <c r="F77">
-        <v>-0.4516152864775618</v>
+        <v>0.4571385458244134</v>
       </c>
       <c r="G77">
-        <v>-2.695824276884219</v>
+        <v>-2.439236032157202</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.078009506605378</v>
       </c>
       <c r="E78">
-        <v>-8.933087270990518</v>
+        <v>-10.68096955457509</v>
       </c>
       <c r="F78">
-        <v>-0.3989510004771805</v>
+        <v>0.28665307902165</v>
       </c>
       <c r="G78">
-        <v>-1.751268870231547</v>
+        <v>-2.225654758409826</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.093037810170719</v>
       </c>
       <c r="E79">
-        <v>-10.21964032199169</v>
+        <v>-11.30097651638726</v>
       </c>
       <c r="F79">
-        <v>-0.2618735910293211</v>
+        <v>0.03517233267535926</v>
       </c>
       <c r="G79">
-        <v>-2.183477936484724</v>
+        <v>-2.434353574476748</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.124892898800196</v>
       </c>
       <c r="E80">
-        <v>-10.55632783598797</v>
+        <v>-11.44677526553822</v>
       </c>
       <c r="F80">
-        <v>-0.3615063087684344</v>
+        <v>0.4148437629722763</v>
       </c>
       <c r="G80">
-        <v>-1.616013636329676</v>
+        <v>-2.595041556685874</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.168561560234645</v>
       </c>
       <c r="E81">
-        <v>-10.7450927465237</v>
+        <v>-11.77274388155834</v>
       </c>
       <c r="F81">
-        <v>-0.6936998613738977</v>
+        <v>-0.05943053819395548</v>
       </c>
       <c r="G81">
-        <v>-1.490027853333237</v>
+        <v>-1.48817724437371</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.232722526511832</v>
       </c>
       <c r="E82">
-        <v>-12.50495737233257</v>
+        <v>-13.53777549620997</v>
       </c>
       <c r="F82">
-        <v>-0.7433116134949629</v>
+        <v>0.05632055246883064</v>
       </c>
       <c r="G82">
-        <v>-1.916612905833526</v>
+        <v>-1.548929061546829</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.315422040981598</v>
       </c>
       <c r="E83">
-        <v>-11.98757468848223</v>
+        <v>-14.18353588970376</v>
       </c>
       <c r="F83">
-        <v>-0.7550479228578263</v>
+        <v>-0.2682661022767249</v>
       </c>
       <c r="G83">
-        <v>-1.502309465630238</v>
+        <v>-1.357653531960559</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.423091025187961</v>
       </c>
       <c r="E84">
-        <v>-14.16826134687589</v>
+        <v>-14.72087555850591</v>
       </c>
       <c r="F84">
-        <v>-0.7629853393114512</v>
+        <v>0.300299603615369</v>
       </c>
       <c r="G84">
-        <v>-1.319634017751273</v>
+        <v>-1.140029793251947</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.556456914027954</v>
       </c>
       <c r="E85">
-        <v>-14.97657584334902</v>
+        <v>-15.43658728999619</v>
       </c>
       <c r="F85">
-        <v>-0.6993460135913792</v>
+        <v>-0.03872052475656505</v>
       </c>
       <c r="G85">
-        <v>-1.59472178963044</v>
+        <v>-1.507241141634084</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.718981483847564</v>
       </c>
       <c r="E86">
-        <v>-15.34826393295058</v>
+        <v>-17.2295414753791</v>
       </c>
       <c r="F86">
-        <v>-0.8525103180016049</v>
+        <v>-0.451061108685089</v>
       </c>
       <c r="G86">
-        <v>-1.238256441855484</v>
+        <v>-1.262186390688515</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.913762882879114</v>
       </c>
       <c r="E87">
-        <v>-16.94026255576912</v>
+        <v>-18.69140081216521</v>
       </c>
       <c r="F87">
-        <v>-0.6883626901976605</v>
+        <v>-0.188967319174131</v>
       </c>
       <c r="G87">
-        <v>-1.104674630948931</v>
+        <v>-0.164519342407474</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.140540608686845</v>
       </c>
       <c r="E88">
-        <v>-19.18267684336134</v>
+        <v>-19.31095039810261</v>
       </c>
       <c r="F88">
-        <v>-0.6414141392765957</v>
+        <v>-0.02633477534990683</v>
       </c>
       <c r="G88">
-        <v>-0.6955259898155313</v>
+        <v>-0.1569725328207512</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.405148261064896</v>
       </c>
       <c r="E89">
-        <v>-20.74834238982527</v>
+        <v>-21.74803019786255</v>
       </c>
       <c r="F89">
-        <v>-0.8421217624030963</v>
+        <v>0.3400165071099941</v>
       </c>
       <c r="G89">
-        <v>-1.057093637115423</v>
+        <v>-0.5110327451926333</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.703963246595489</v>
       </c>
       <c r="E90">
-        <v>-21.84683697223591</v>
+        <v>-23.90241095074565</v>
       </c>
       <c r="F90">
-        <v>-1.046119660853517</v>
+        <v>-0.01476413946760334</v>
       </c>
       <c r="G90">
-        <v>-0.9245388485569752</v>
+        <v>-0.29743834655902</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.04700148979926</v>
       </c>
       <c r="E91">
-        <v>-23.34028694369952</v>
+        <v>-24.33094950303951</v>
       </c>
       <c r="F91">
-        <v>-0.8857866649394639</v>
+        <v>-0.1182703031822072</v>
       </c>
       <c r="G91">
-        <v>-1.181763650266525</v>
+        <v>-1.114393609208006</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.42719849858564</v>
       </c>
       <c r="E92">
-        <v>-25.97896534933293</v>
+        <v>-27.42158320006045</v>
       </c>
       <c r="F92">
-        <v>-1.015164399378302</v>
+        <v>0.2942301556550571</v>
       </c>
       <c r="G92">
-        <v>-0.5397664023886907</v>
+        <v>-0.7718668906175721</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.8571904238904</v>
       </c>
       <c r="E93">
-        <v>-27.51522298559106</v>
+        <v>-28.07898630022796</v>
       </c>
       <c r="F93">
-        <v>-1.080289816218996</v>
+        <v>-0.1683028659438945</v>
       </c>
       <c r="G93">
-        <v>-0.9276756963678043</v>
+        <v>0.05232674679154888</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.32344144548374</v>
       </c>
       <c r="E94">
-        <v>-30.28313271821836</v>
+        <v>-29.9407325342614</v>
       </c>
       <c r="F94">
-        <v>-0.8543459801662087</v>
+        <v>-0.02861361407500828</v>
       </c>
       <c r="G94">
-        <v>-0.7616655727892584</v>
+        <v>-0.8395978660476299</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.83627919780754</v>
       </c>
       <c r="E95">
-        <v>-32.0169450330611</v>
+        <v>-32.48605191975268</v>
       </c>
       <c r="F95">
-        <v>-0.8889104384154208</v>
+        <v>-0.1013053387728733</v>
       </c>
       <c r="G95">
-        <v>-1.055787710934764</v>
+        <v>-1.669802701353654</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.38059456220514</v>
       </c>
       <c r="E96">
-        <v>-34.19228809212571</v>
+        <v>-35.1404984718808</v>
       </c>
       <c r="F96">
-        <v>-0.8213429944712736</v>
+        <v>-0.05677147883096907</v>
       </c>
       <c r="G96">
-        <v>-1.539639923312041</v>
+        <v>-0.1172402209574351</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.95827052601345</v>
       </c>
       <c r="E97">
-        <v>-37.41211915258548</v>
+        <v>-37.73794059320036</v>
       </c>
       <c r="F97">
-        <v>-0.8706258847334274</v>
+        <v>-0.002484421088503469</v>
       </c>
       <c r="G97">
-        <v>-1.344049587375101</v>
+        <v>-1.405313275111493</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-13.55631835980067</v>
       </c>
       <c r="E98">
-        <v>-39.78399798358299</v>
+        <v>-40.01418258162987</v>
       </c>
       <c r="F98">
-        <v>-0.8649474261872367</v>
+        <v>-0.03417113098039016</v>
       </c>
       <c r="G98">
-        <v>-1.843454789944146</v>
+        <v>-1.644878542388111</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-14.16192318215194</v>
       </c>
       <c r="E99">
-        <v>-41.5996783157734</v>
+        <v>-41.46889145795787</v>
       </c>
       <c r="F99">
-        <v>-0.9472970864343412</v>
+        <v>-0.2772737694147667</v>
       </c>
       <c r="G99">
-        <v>-2.023295262395751</v>
+        <v>-1.646476497287561</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-14.77405200459079</v>
       </c>
       <c r="E100">
-        <v>-44.33897941385724</v>
+        <v>-45.11384886554671</v>
       </c>
       <c r="F100">
-        <v>-1.108934761007803</v>
+        <v>-0.01115659942841149</v>
       </c>
       <c r="G100">
-        <v>-2.413747503083435</v>
+        <v>-1.858518878123557</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-15.351609450212</v>
       </c>
       <c r="E101">
-        <v>-46.42462698825192</v>
+        <v>-46.5779362115446</v>
       </c>
       <c r="F101">
-        <v>-0.8570920181064891</v>
+        <v>-0.6351583086506539</v>
       </c>
       <c r="G101">
-        <v>-3.068449640839439</v>
+        <v>-2.772063459817917</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-15.93412528680131</v>
       </c>
       <c r="E102">
-        <v>-49.2728729818938</v>
+        <v>-49.65010732003626</v>
       </c>
       <c r="F102">
-        <v>-0.5502738441509829</v>
+        <v>-0.4128584608027813</v>
       </c>
       <c r="G102">
-        <v>-2.965137098818763</v>
+        <v>-2.50932948711006</v>
       </c>
     </row>
   </sheetData>
